--- a/AAII_Financials/Quarterly/WFC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WFC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
   <si>
     <t>WFC</t>
   </si>
@@ -656,271 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21708000</v>
+      </c>
+      <c r="E8" s="3">
         <v>20311000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20252000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20755000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19817000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19217000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19283000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19301000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19453000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19925000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19196000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19660000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18820000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19522000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>17793000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14494000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11556000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10181000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10121000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9834000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9693000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10046000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10550000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10811000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11813000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>14745000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>15595000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16499000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>16986000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>17003000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>16921000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>16364000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>16015000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>15347000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>14958000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>15044000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>14694000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>14213000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>14058000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>13487000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>21708000</v>
+      </c>
+      <c r="E10" s="3">
         <v>20311000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20252000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20755000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19817000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19217000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19283000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19301000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19453000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19925000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19196000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19660000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18820000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19522000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,52 +1467,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>-463000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>89000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>122000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>15000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>76000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>135000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>2079000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1573,53 +1592,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1877000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1836000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2123000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1839000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1893000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1858000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1984000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1783000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1972000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1819000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1494000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1597000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1628000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1552000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1629,8 +1651,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>5</v>
@@ -1647,56 +1669,59 @@
       <c r="Z15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB15" s="3">
         <v>-22000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-23000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-26000</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>-27000</v>
       </c>
       <c r="AE15" s="3">
         <v>-27000</v>
       </c>
       <c r="AF15" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="AG15" s="3">
         <v>-28000</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>-264000</v>
       </c>
       <c r="AH15" s="3">
         <v>-264000</v>
       </c>
       <c r="AI15" s="3">
-        <v>-265000</v>
+        <v>-264000</v>
       </c>
       <c r="AJ15" s="3">
         <v>-265000</v>
       </c>
       <c r="AK15" s="3">
-        <v>-288000</v>
+        <v>-265000</v>
       </c>
       <c r="AL15" s="3">
         <v>-288000</v>
       </c>
       <c r="AM15" s="3">
+        <v>-288000</v>
+      </c>
+      <c r="AN15" s="3">
         <v>-287000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-289000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-301000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-299000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13592000</v>
+      </c>
+      <c r="E17" s="3">
         <v>14330000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14189000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13757000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13257000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13891000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13885000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12991000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13158000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14338000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13707000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13113000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12987000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13676000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5317000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3180000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1938000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>173000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>407000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-470000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-367000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>190000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1016000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2201000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>11455000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7420000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5039000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5569000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5394000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5537000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4798000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4372000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3926000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3300000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3296000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3312000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2778000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2494000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2461000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2340000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8116000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5981000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6063000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6998000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6560000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5326000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5398000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6310000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6295000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5587000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5489000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6547000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5833000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5846000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12476000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11314000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9618000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10008000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9714000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10304000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10060000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9856000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9534000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8610000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>358000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>7325000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10556000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10930000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>11592000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>11466000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>12123000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>11992000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>12089000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>12047000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>11662000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>11732000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>11916000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>11719000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>11597000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>11147000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,208 +2101,214 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-9585000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6838000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6020000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5344000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1604000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3378000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1871000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4265000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5668000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5292000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6157000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-6205000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6954000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-4814000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3960000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-4618000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-5003000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-4394000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-4970000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-5346000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-7063000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-4951000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-3777000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-3861000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-4035000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-2892000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9993000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7817000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8186000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8837000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8453000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7184000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7382000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8093000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8267000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7406000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6983000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8144000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7461000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7398000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4470000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6166000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5370000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6455000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9910000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8843000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>10125000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7828000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6158000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5904000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3809000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2988000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>5737000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>7956000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9283000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>8297000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>8491000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>8985000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>8523000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>8132000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>6211000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>8097000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>9380000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>9095000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>8934000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>9620000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8047000</v>
+      </c>
+      <c r="E23" s="3">
         <v>5981000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6526000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6909000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6438000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5326000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5383000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6234000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6160000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5587000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3410000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6547000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5833000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5846000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2891000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4476000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3598000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4664000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8110000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6926000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8189000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5591000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3866000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3318000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5799000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1120000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3602000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6116000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>7632000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>6848000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>7120000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>7598000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>7119000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>6701000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>4599000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>6781000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>8139000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>7858000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>7562000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>8255000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1402000</v>
+      </c>
+      <c r="E24" s="3">
         <v>691000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1103000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>916000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>522000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>120000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1064000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1251000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>964000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>811000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>930000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>966000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-29000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>912000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>622000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>746000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1711000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1521000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1445000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>901000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>574000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-83000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-2001000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>353000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>678000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1304000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1294000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>881000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>970000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1344000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1810000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1374000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>775000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>2181000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>2245000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>2133000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>2258000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>2601000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6645000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5290000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5423000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5609000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5522000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4804000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5263000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5170000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4909000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4623000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3510000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5736000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4903000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4880000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2920000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3564000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2976000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3918000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6399000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5405000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6744000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4690000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3292000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3401000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3798000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>767000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2924000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4812000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>6338000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5967000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6150000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>6254000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>5309000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>5327000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3824000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>4600000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>5894000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>5725000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>5304000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>5654000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6160000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5000000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5114000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5341000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5214000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4616000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4801000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4852000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4640000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4313000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3160000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5450000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4659000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4713000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2877000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3313000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2863000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3509000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5470000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4787000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5743000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4256000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2741000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2901000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4160000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>304000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2546000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4037000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5848000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5507000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5707000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>5621000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4792000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4733000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3323000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>4131000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>5450000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>5233000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>4872000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>5243000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3196,17 +3256,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -3214,24 +3274,24 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>4000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-168000</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>2417000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,208 +3601,214 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>9585000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6838000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6020000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5344000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1604000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3378000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1871000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4265000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5668000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5292000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6157000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>6205000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6954000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>4814000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3960000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>4618000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>5003000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>4394000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>4970000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>5346000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>7063000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>4951000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>3777000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>3861000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>4035000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>2892000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6407000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5253000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5361000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5589000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5494000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4894000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5079000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5114000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4910000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4619000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3446000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5767000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4938000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4991000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2877000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3313000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2863000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3509000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5470000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4787000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5743000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4256000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2741000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2901000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4160000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>304000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2546000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4037000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5848000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5507000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5711000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>5453000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4792000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4733000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>5740000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>4131000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>5450000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>5233000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>4872000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>5243000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6407000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5253000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5361000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5589000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5494000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4894000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5079000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5114000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4910000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4619000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3446000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5767000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4938000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4991000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2877000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3313000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2863000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3509000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5470000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4787000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5743000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4256000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2741000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2901000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4160000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>304000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2546000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4037000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5848000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5507000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5711000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>5453000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4792000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4733000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>5740000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>4131000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>5450000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>5233000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>4872000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>5243000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,297 +4276,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>200464000</v>
+      </c>
+      <c r="E41" s="3">
         <v>387478000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>365178000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>325673000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>296677000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>301736000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>306009000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>288340000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>311917000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>337237000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>316459000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>287530000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>219999000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>222928000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>34596000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>27634000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>29716000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>27454000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>24616000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>25509000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>25304000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>28339000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>28236000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>25535000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>24704000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>22738000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>21757000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>22401000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>20880000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>20650000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>23551000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>18791000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>20450000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>18145000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>23367000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>19206000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>20248000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>19698000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>20729000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>19287000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>295948000</v>
+      </c>
+      <c r="E42" s="3">
         <v>73722000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>84033000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>92086000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>85449000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>80547000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>74138000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>76970000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>77433000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>74130000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>71437000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>78334000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>146089000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>87156000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>343166000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>338987000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>331901000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>399632000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>436988000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>470454000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>466292000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>470661000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>437151000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>414961000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>444261000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>349008000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>369607000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>372378000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>387411000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>355757000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>355080000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>351146000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>346290000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>376601000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>364934000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>361509000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>348313000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>389073000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>340435000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>384271000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27325000</v>
+      </c>
+      <c r="E43" s="3">
         <v>26355000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>19651000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20882000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>34809000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>28596000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19608000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28977000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21243000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>32440000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>30541000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>28340000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>30599000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>29887000</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4557,53 +4649,56 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E44" s="3">
         <v>299000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>302000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>218000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>207000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>247000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>206000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>212000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>216000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>165000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>187000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>177000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>133000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>132000</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>161562000</v>
+      </c>
+      <c r="E45" s="3">
         <v>156307000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>152381000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>126662000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>102140000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>94055000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>102251000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>89833000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>90485000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>78981000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>69297000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>64763000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6134000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>55375000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>689400000</v>
+      </c>
+      <c r="E46" s="3">
         <v>650206000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>627371000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>578491000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>529283000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>512884000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>506108000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>492785000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>509728000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>529587000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>494073000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>464249000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>409902000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>402468000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,53 +5024,56 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>487656000</v>
+      </c>
+      <c r="E47" s="3">
         <v>464524000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>458967000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>456681000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>441913000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>440177000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>435742000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>445017000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>436009000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>433644000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>428543000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>426399000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>439203000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>454179000</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5045,252 +5149,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15975000</v>
+      </c>
+      <c r="E48" s="3">
         <v>15840000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20035000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19797000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19622000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19311000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19433000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>18977000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18873000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18385000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18236000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17603000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17561000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17831000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12187000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12297000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12279000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12255000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12376000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12589000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12798000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12897000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13201000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13398000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13573000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13758000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>14033000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>14171000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>14211000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13694000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8920000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8802000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8882000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8828000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8847000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8449000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>8403000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>8320000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>8333000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>8322000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>30904000</v>
+      </c>
+      <c r="E49" s="3">
         <v>31183000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>31294000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>31854000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>32119000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>32246000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>32946000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>32666000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>33199000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>33421000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>33683000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>34832000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>34520000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>35123000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>35805000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>36366000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>35745000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>35130000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>33580000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>34606000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>34490000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>35430000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>40282000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>34419000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>34940000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>36312000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>39760000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>39308000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>40397000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>41691000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>43055000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>44631000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>44324000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>44240000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>43246000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>43224000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>42894000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>43711000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>43767000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>41463000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,53 +5649,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>41056000</v>
+      </c>
+      <c r="E52" s="3">
         <v>41076000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>38594000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>46745000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>47875000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>45880000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>37054000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>37299000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38717000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35753000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35857000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>38308000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>41432000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>41928000</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5655,8 +5774,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2282201000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2205752000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2148631000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2062926000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1981269000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1950311000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1929845000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1922125000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1940073000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1959153000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1932468000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1909261000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1876320000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1886400000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1881020000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1877745000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1881142000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1939709000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1948068000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1954901000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1945996000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1959543000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1952911000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1922220000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1968766000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1981349000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1927555000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1943950000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1923388000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1887792000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1895883000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1872981000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1879700000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1915388000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1951757000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1934939000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1930871000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1951564000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1930115000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>1942124000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,53 +6116,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1501405000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1454939000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1426207000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1367361000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1340703000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1361728000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1371804000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1349646000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1365894000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1383147000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1358173000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1354010000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1344584000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1362629000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6109,53 +6239,56 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>305077000</v>
+      </c>
+      <c r="E58" s="3">
         <v>303427000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>289006000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>242957000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>208530000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>162669000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>117274000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>123402000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>137905000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>131119000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>108054000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>120258000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>112148000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>113456000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6231,32 +6364,35 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>41410000</v>
+      </c>
+      <c r="E59" s="3">
         <v>39161000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>31844000</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3">
         <v>28478000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6275,131 +6411,134 @@
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>68740000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>72991000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>71662000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>74229000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>70957000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>75513000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>72555000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>76914000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>74360000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>72271000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>75159000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>76238000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>75163000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>76532000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>69706000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>74717000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>69317000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>71348000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>72480000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>73397000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>70615000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>79208000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>73035000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>59831000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>57189000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>82769000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1919885000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1854042000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1805391000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1693334000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1620035000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1595410000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1567878000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1550962000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1581211000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1589636000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1532746000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1536148000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1525936000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1540885000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,154 +6614,160 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>173393000</v>
+      </c>
+      <c r="E61" s="3">
         <v>165797000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>154502000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>181180000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>172480000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>166195000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>174501000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>186152000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>180714000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>186843000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>211648000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>190740000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>168432000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>162295000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>174870000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>156412000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>150291000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>153337000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>160689000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>162982000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>179656000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>183312000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>212950000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>215711000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>230921000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>237342000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>228191000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>230651000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>241476000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>236339000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>229044000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>221323000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>219284000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>227302000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>225020000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>238893000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>238869000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>256468000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>255077000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>254835000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6600000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5600000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5700000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5400000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>5800000</v>
       </c>
       <c r="H62" s="3">
         <v>5800000</v>
       </c>
       <c r="I62" s="3">
+        <v>5800000</v>
+      </c>
+      <c r="J62" s="3">
         <v>6400000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
@@ -6641,8 +6786,8 @@
       <c r="P62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -6719,8 +6864,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2099878000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2025439000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1965593000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1879914000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1798315000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1767405000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1748779000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1737114000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1761925000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1776479000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1745025000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1726888000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1694368000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1703180000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1700793000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1701556000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1703610000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1760466000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1760462000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1765873000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1754734000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1772325000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1768231000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1741047000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1789380000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1798631000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1740409000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1750646000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1724346000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1689960000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1699717000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1674240000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1674512000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1710436000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1744821000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1729010000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1725641000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1750064000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1730534000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1739096000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7504,7 +7671,7 @@
         <v>15348000</v>
       </c>
       <c r="E70" s="3">
-        <v>16608000</v>
+        <v>15348000</v>
       </c>
       <c r="F70" s="3">
         <v>16608000</v>
@@ -7513,7 +7680,7 @@
         <v>16608000</v>
       </c>
       <c r="H70" s="3">
-        <v>18608000</v>
+        <v>16608000</v>
       </c>
       <c r="I70" s="3">
         <v>18608000</v>
@@ -7522,16 +7689,16 @@
         <v>18608000</v>
       </c>
       <c r="K70" s="3">
+        <v>18608000</v>
+      </c>
+      <c r="L70" s="3">
         <v>16608000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>18608000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>19448000</v>
-      </c>
-      <c r="N70" s="3">
-        <v>19019000</v>
       </c>
       <c r="O70" s="3">
         <v>19019000</v>
@@ -7540,10 +7707,10 @@
         <v>19019000</v>
       </c>
       <c r="Q70" s="3">
+        <v>19019000</v>
+      </c>
+      <c r="R70" s="3">
         <v>19448000</v>
-      </c>
-      <c r="R70" s="3">
-        <v>20057000</v>
       </c>
       <c r="S70" s="3">
         <v>20057000</v>
@@ -7555,70 +7722,73 @@
         <v>20057000</v>
       </c>
       <c r="V70" s="3">
+        <v>20057000</v>
+      </c>
+      <c r="W70" s="3">
         <v>20270000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>20820000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>21170000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>21136000</v>
-      </c>
-      <c r="Z70" s="3">
-        <v>21098000</v>
       </c>
       <c r="AA70" s="3">
         <v>21098000</v>
       </c>
       <c r="AB70" s="3">
+        <v>21098000</v>
+      </c>
+      <c r="AC70" s="3">
         <v>21347000</v>
-      </c>
-      <c r="AC70" s="3">
-        <v>21549000</v>
       </c>
       <c r="AD70" s="3">
         <v>21549000</v>
       </c>
       <c r="AE70" s="3">
+        <v>21549000</v>
+      </c>
+      <c r="AF70" s="3">
         <v>23021000</v>
-      </c>
-      <c r="AF70" s="3">
-        <v>23214000</v>
       </c>
       <c r="AG70" s="3">
         <v>23214000</v>
       </c>
       <c r="AH70" s="3">
+        <v>23214000</v>
+      </c>
+      <c r="AI70" s="3">
         <v>23482000</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>25737000</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>26227000</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AL70" s="3">
         <v>25358000</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AM70" s="3">
         <v>25576000</v>
       </c>
-      <c r="AM70" s="3">
+      <c r="AN70" s="3">
         <v>25785000</v>
       </c>
-      <c r="AN70" s="3">
+      <c r="AO70" s="3">
         <v>25501000</v>
       </c>
-      <c r="AO70" s="3">
+      <c r="AP70" s="3">
         <v>24551000</v>
       </c>
-      <c r="AP70" s="3">
+      <c r="AQ70" s="3">
         <v>24594000</v>
       </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>237230000</v>
+      </c>
+      <c r="E72" s="3">
         <v>232459000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>228873000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>225189000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>221308000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>217405000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>214198000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>210749000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>207281000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>203870000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>201136000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>199287000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>195164000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>191688000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>187968000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>186551000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>184475000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>182623000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>180322000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>175709000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>171765000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>166772000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>162683000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>160913000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>159952000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>165308000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>166697000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>166320000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>164551000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>160776000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>158163000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>154576000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>150803000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>147928000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>145263000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>141761000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>139524000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>136032000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>133075000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>130288000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>164842000</v>
+      </c>
+      <c r="E76" s="3">
         <v>163048000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>164509000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>164546000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>164503000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>162482000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>160512000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>164657000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>159822000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>162335000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>166287000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>161696000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>161172000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>162149000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>160779000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>156132000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>157475000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>159186000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>167549000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>168758000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>170442000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>166048000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>163544000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>160075000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>158288000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>161371000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>165597000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>171755000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>176021000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>174618000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>172952000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>175259000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>179451000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>178725000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>181578000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>180353000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>179445000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>175999000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>175030000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>178434000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6407000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5253000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5361000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5589000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5494000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4894000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5079000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5114000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4910000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4619000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3446000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5767000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4938000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4991000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2877000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3313000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2863000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3509000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5470000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4787000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5743000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4256000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2741000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2901000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4160000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>304000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2546000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4037000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5848000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5507000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5711000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>5453000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4792000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4733000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>5740000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>4131000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>5450000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>5233000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>4872000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>5243000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1857000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1809000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1926000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1725000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1914000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1762000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1438000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1538000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1566000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1491000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1517000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1628000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1708000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1732000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1579000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1690000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1772000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1791000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1800000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1917000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1936000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2237000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2292000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2382000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2194000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1868000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2135000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1840000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1651000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1449000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1371000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1387000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1404000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1431000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1612000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1316000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1241000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1237000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1372000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>1365000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6775000</v>
+      </c>
+      <c r="E89" s="3">
         <v>9143000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4121000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-869000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11216000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11037000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8904000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4206000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2050000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-12125000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>18202000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>15505000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-755000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7406000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7245000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>12016000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>7588000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>199000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4817000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4810000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-8062000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3470000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-22765000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-8576000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>16119000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>17273000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>12423000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-12975000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-669000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7951000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>15034000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>6658000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-849000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>15230000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>242000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>9522000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-4233000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>13191000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>4764000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-2397000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9926,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9784,8 +10004,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-29870000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-55567000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-85570000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-82865000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>8048000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27508000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1064000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-21098000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14584000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>21095000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4231000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>7628000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>20601000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7955000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15926000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>919000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4508000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-22961000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-31402000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7021000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>15276000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>15528000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>20512000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>42658000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>103687000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-44303000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2526000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7381000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-10698000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-9026000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-18245000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-220000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>550000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>10161000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-19948000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>2184000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>14499000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1899000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-12931000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-39684000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,130 +10426,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1366000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1387000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1398000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1431000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1287000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1318000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1325000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1357000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1204000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>1247000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>1265000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>1275000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>1112000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>1137000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1138000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1136000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-946000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-958000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-819000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-808000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-412000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-383000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-398000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-399000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-2023000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-2032000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-2080000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-2164000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1957000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1997000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1962000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-2008000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1855000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1867000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1875000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1890000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1856000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-1863000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-1870000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,130 +10924,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>51283000</v>
+      </c>
+      <c r="E100" s="3">
         <v>47104000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>81526000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>63117000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>20123000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12821000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9934000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-29760000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-25282000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>23574000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5365000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>39165000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-21859000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2177000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2383000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2620000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-49835000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-9573000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5872000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4345000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-19774000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>10063000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>20095000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-49815000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-8112000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>36589000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-17378000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>4660000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>26826000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-23244000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>16975000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-10364000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-38647000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-38943000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>18397000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-7278000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-37090000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>15051000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>9691000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>41005000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>28188000</v>
+      </c>
+      <c r="E102" s="3">
         <v>680000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>77000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-20617000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>16955000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25724000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>17774000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-46652000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-37816000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>32544000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19336000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>62298000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2013000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2726000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6298000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>10315000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-46755000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-32335000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-32457000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-7486000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-12560000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>22121000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>17842000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-15733000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>111694000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>9559000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-7481000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-15696000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>15459000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-24319000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>13764000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3926000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-38946000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-13552000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1173000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>4292000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-26771000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>26290000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1442000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-1120000</v>
       </c>
     </row>
